--- a/AAII_Financials/Yearly/LOOP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LOOP_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
   <si>
     <t>LOOP</t>
   </si>
@@ -786,8 +786,8 @@
       <c r="D9" s="3">
         <v>400</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>4</v>
+      <c r="E9" s="3">
+        <v>200</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>4</v>
@@ -838,7 +838,7 @@
         <v>100</v>
       </c>
       <c r="E10" s="3">
-        <v>10900</v>
+        <v>10700</v>
       </c>
       <c r="F10" s="3">
         <v>200</v>
@@ -910,7 +910,7 @@
         <v>3500</v>
       </c>
       <c r="E12" s="3">
-        <v>6900</v>
+        <v>6600</v>
       </c>
       <c r="F12" s="3">
         <v>11400</v>
@@ -1252,7 +1252,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>700</v>
+        <v>2200</v>
       </c>
       <c r="E20" s="3">
         <v>800</v>
@@ -1303,7 +1303,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-10400</v>
+        <v>-12000</v>
       </c>
       <c r="E21" s="3">
         <v>-6100</v>
@@ -1354,7 +1354,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1700</v>
+        <v>200</v>
       </c>
       <c r="E22" s="3">
         <v>300</v>
@@ -1864,7 +1864,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-700</v>
+        <v>-2200</v>
       </c>
       <c r="E32" s="3">
         <v>-800</v>
@@ -2318,8 +2318,8 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>4</v>
+      <c r="D44" s="3">
+        <v>0</v>
       </c>
       <c r="E44" s="3">
         <v>100</v>
@@ -2369,8 +2369,8 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>4</v>
+      <c r="D45" s="3">
+        <v>200</v>
       </c>
       <c r="E45" s="3">
         <v>100</v>
@@ -2922,7 +2922,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1900</v>
+        <v>700</v>
       </c>
       <c r="E57" s="3">
         <v>2000</v>
@@ -4091,7 +4091,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>300</v>
